--- a/xlsx/Power/p13.xlsx
+++ b/xlsx/Power/p13.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36151901-00D0-462B-B44E-A128F00A6380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1008A419-63FB-4131-B7BD-E2C9BD66A1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{650C834A-63C4-431E-8D10-BB176D084CCD}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{650C834A-63C4-431E-8D10-BB176D084CCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,25 +404,25 @@
         <v>0.51300000000000001</v>
       </c>
       <c r="C1">
-        <v>0.70299999999999996</v>
+        <v>0.254</v>
       </c>
       <c r="D1">
-        <v>0.86699999999999999</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="E1">
-        <v>0.92200000000000004</v>
+        <v>0.752</v>
       </c>
       <c r="F1">
-        <v>0.96199999999999997</v>
+        <v>0.878</v>
       </c>
       <c r="G1">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="H1">
         <v>0.97299999999999998</v>
       </c>
-      <c r="H1">
-        <v>0.995</v>
-      </c>
       <c r="I1">
-        <v>0.997</v>
+        <v>0.99</v>
       </c>
       <c r="J1">
         <v>0.999</v>
@@ -436,28 +436,28 @@
         <v>0.49399999999999999</v>
       </c>
       <c r="C2">
-        <v>0.68300000000000005</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="D2">
-        <v>0.84799999999999998</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="E2">
-        <v>0.90100000000000002</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="F2">
-        <v>0.94499999999999995</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="G2">
-        <v>0.97199999999999998</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="H2">
-        <v>0.98899999999999999</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="I2">
-        <v>0.995</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="J2">
-        <v>0.999</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,13 +468,13 @@
         <v>0.45600000000000002</v>
       </c>
       <c r="C3">
-        <v>0.64200000000000002</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="D3">
-        <v>0.79</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="E3">
-        <v>0.86699999999999999</v>
+        <v>0.871</v>
       </c>
       <c r="F3">
         <v>0.92600000000000005</v>
@@ -489,27 +489,27 @@
         <v>0.98699999999999999</v>
       </c>
       <c r="J3">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.192</v>
+        <v>0.215</v>
       </c>
       <c r="B4">
-        <v>0.42199999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="C4">
-        <v>0.59199999999999997</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="D4">
-        <v>0.73899999999999999</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="E4">
         <v>0.81699999999999995</v>
       </c>
       <c r="F4">
-        <v>0.89100000000000001</v>
+        <v>0.89200000000000002</v>
       </c>
       <c r="G4">
         <v>0.91400000000000003</v>
@@ -564,28 +564,28 @@
         <v>0.434</v>
       </c>
       <c r="C6">
-        <v>0.60399999999999998</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="D6">
-        <v>0.77700000000000002</v>
+        <v>0.83099999999999996</v>
       </c>
       <c r="E6">
-        <v>0.83799999999999997</v>
+        <v>0.87</v>
       </c>
       <c r="F6">
-        <v>0.89100000000000001</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="G6">
-        <v>0.95199999999999996</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="H6">
-        <v>0.97199999999999998</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I6">
         <v>0.99</v>
       </c>
       <c r="J6">
-        <v>0.996</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,25 +596,25 @@
         <v>0.41599999999999998</v>
       </c>
       <c r="C7">
-        <v>0.57599999999999996</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="D7">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="E7">
-        <v>0.79600000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="F7">
-        <v>0.86799999999999999</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="G7">
-        <v>0.93200000000000005</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="H7">
         <v>0.95299999999999996</v>
       </c>
       <c r="I7">
-        <v>0.98299999999999998</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="J7">
         <v>0.995</v>
@@ -628,28 +628,28 @@
         <v>0.38300000000000001</v>
       </c>
       <c r="C8">
-        <v>0.54400000000000004</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D8">
-        <v>0.65900000000000003</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="E8">
-        <v>0.751</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="F8">
-        <v>0.81</v>
+        <v>0.623</v>
       </c>
       <c r="G8">
-        <v>0.86099999999999999</v>
+        <v>0.72399999999999998</v>
       </c>
       <c r="H8">
-        <v>0.89200000000000002</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="I8">
-        <v>0.96899999999999997</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="J8">
-        <v>0.97299999999999998</v>
+        <v>0.77500000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.249</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D9">
-        <v>0.248</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="E9">
-        <v>0.31</v>
+        <v>0.82</v>
       </c>
       <c r="F9">
-        <v>0.374</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="G9">
-        <v>0.40400000000000003</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="H9">
-        <v>0.443</v>
+        <v>0.501</v>
       </c>
       <c r="I9">
-        <v>0.504</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="J9">
-        <v>0.54800000000000004</v>
+        <v>0.56499999999999995</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p13.xlsx
+++ b/xlsx/Power/p13.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1008A419-63FB-4131-B7BD-E2C9BD66A1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD5E3BF-51A1-46E4-9272-20848ED4F7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{650C834A-63C4-431E-8D10-BB176D084CCD}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{650C834A-63C4-431E-8D10-BB176D084CCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,25 +404,25 @@
         <v>0.51300000000000001</v>
       </c>
       <c r="C1">
-        <v>0.254</v>
+        <v>0.70299999999999996</v>
       </c>
       <c r="D1">
-        <v>0.55300000000000005</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="E1">
-        <v>0.752</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="F1">
-        <v>0.878</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="G1">
-        <v>0.93799999999999994</v>
+        <v>0.97299999999999998</v>
       </c>
       <c r="H1">
-        <v>0.97299999999999998</v>
+        <v>0.995</v>
       </c>
       <c r="I1">
-        <v>0.99</v>
+        <v>0.997</v>
       </c>
       <c r="J1">
         <v>0.999</v>
@@ -436,28 +436,28 @@
         <v>0.49399999999999999</v>
       </c>
       <c r="C2">
-        <v>0.25800000000000001</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="D2">
-        <v>0.54800000000000004</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="E2">
-        <v>0.73799999999999999</v>
+        <v>0.90100000000000002</v>
       </c>
       <c r="F2">
-        <v>0.85499999999999998</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="G2">
-        <v>0.93300000000000005</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="H2">
-        <v>0.96799999999999997</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="I2">
-        <v>0.98599999999999999</v>
+        <v>0.995</v>
       </c>
       <c r="J2">
-        <v>0.996</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,13 +468,13 @@
         <v>0.45600000000000002</v>
       </c>
       <c r="C3">
-        <v>0.67600000000000005</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="D3">
-        <v>0.79700000000000004</v>
+        <v>0.79</v>
       </c>
       <c r="E3">
-        <v>0.871</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="F3">
         <v>0.92600000000000005</v>
@@ -489,27 +489,27 @@
         <v>0.98699999999999999</v>
       </c>
       <c r="J3">
-        <v>0.997</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.215</v>
+        <v>0.192</v>
       </c>
       <c r="B4">
-        <v>0.44</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="C4">
-        <v>0.59499999999999997</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="D4">
-        <v>0.73799999999999999</v>
+        <v>0.73899999999999999</v>
       </c>
       <c r="E4">
         <v>0.81699999999999995</v>
       </c>
       <c r="F4">
-        <v>0.89200000000000002</v>
+        <v>0.89100000000000001</v>
       </c>
       <c r="G4">
         <v>0.91400000000000003</v>
@@ -564,28 +564,28 @@
         <v>0.434</v>
       </c>
       <c r="C6">
-        <v>0.78300000000000003</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="D6">
-        <v>0.83099999999999996</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="E6">
-        <v>0.87</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="F6">
-        <v>0.90600000000000003</v>
+        <v>0.89100000000000001</v>
       </c>
       <c r="G6">
-        <v>0.95599999999999996</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="H6">
-        <v>0.97499999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="I6">
         <v>0.99</v>
       </c>
       <c r="J6">
-        <v>0.998</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,25 +596,25 @@
         <v>0.41599999999999998</v>
       </c>
       <c r="C7">
-        <v>0.57299999999999995</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="D7">
-        <v>0.745</v>
+        <v>0.748</v>
       </c>
       <c r="E7">
-        <v>0.8</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="F7">
-        <v>0.86699999999999999</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="G7">
-        <v>0.92900000000000005</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="H7">
         <v>0.95299999999999996</v>
       </c>
       <c r="I7">
-        <v>0.98199999999999998</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="J7">
         <v>0.995</v>
@@ -628,28 +628,28 @@
         <v>0.38300000000000001</v>
       </c>
       <c r="C8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="D8">
-        <v>0.20899999999999999</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="E8">
-        <v>0.45800000000000002</v>
+        <v>0.751</v>
       </c>
       <c r="F8">
-        <v>0.623</v>
+        <v>0.81</v>
       </c>
       <c r="G8">
-        <v>0.72399999999999998</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="H8">
-        <v>0.81799999999999995</v>
+        <v>0.89200000000000002</v>
       </c>
       <c r="I8">
-        <v>0.73799999999999999</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="J8">
-        <v>0.77500000000000002</v>
+        <v>0.97299999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.249</v>
       </c>
       <c r="C9">
-        <v>0.55000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>0.93899999999999995</v>
+        <v>0.248</v>
       </c>
       <c r="E9">
-        <v>0.82</v>
+        <v>0.31</v>
       </c>
       <c r="F9">
-        <v>0.51200000000000001</v>
+        <v>0.374</v>
       </c>
       <c r="G9">
-        <v>0.47899999999999998</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="H9">
-        <v>0.501</v>
+        <v>0.443</v>
       </c>
       <c r="I9">
-        <v>0.52700000000000002</v>
+        <v>0.504</v>
       </c>
       <c r="J9">
-        <v>0.56499999999999995</v>
+        <v>0.54800000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p13.xlsx
+++ b/xlsx/Power/p13.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD5E3BF-51A1-46E4-9272-20848ED4F7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392BC1B4-672B-4C55-A1BE-6687A5F5F41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{650C834A-63C4-431E-8D10-BB176D084CCD}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{650C834A-63C4-431E-8D10-BB176D084CCD}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.219</v>
+        <v>0.218</v>
       </c>
       <c r="B1">
         <v>0.51300000000000001</v>
       </c>
       <c r="C1">
-        <v>0.70299999999999996</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="D1">
-        <v>0.86699999999999999</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="E1">
-        <v>0.92200000000000004</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="F1">
         <v>0.96199999999999997</v>
@@ -419,7 +419,7 @@
         <v>0.97299999999999998</v>
       </c>
       <c r="H1">
-        <v>0.995</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="I1">
         <v>0.997</v>
@@ -430,13 +430,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.217</v>
+        <v>0.214</v>
       </c>
       <c r="B2">
-        <v>0.49399999999999999</v>
+        <v>0.495</v>
       </c>
       <c r="C2">
-        <v>0.68300000000000005</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="D2">
         <v>0.84799999999999998</v>
@@ -445,10 +445,10 @@
         <v>0.90100000000000002</v>
       </c>
       <c r="F2">
-        <v>0.94499999999999995</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="G2">
-        <v>0.97199999999999998</v>
+        <v>0.97</v>
       </c>
       <c r="H2">
         <v>0.98899999999999999</v>
@@ -462,19 +462,19 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.19600000000000001</v>
+        <v>0.193</v>
       </c>
       <c r="B3">
         <v>0.45600000000000002</v>
       </c>
       <c r="C3">
-        <v>0.64200000000000002</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="D3">
-        <v>0.79</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="E3">
-        <v>0.86699999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="F3">
         <v>0.92600000000000005</v>
@@ -483,36 +483,36 @@
         <v>0.94699999999999995</v>
       </c>
       <c r="H3">
-        <v>0.98499999999999999</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="I3">
         <v>0.98699999999999999</v>
       </c>
       <c r="J3">
-        <v>0.996</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="B4">
-        <v>0.42199999999999999</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="C4">
-        <v>0.59199999999999997</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="D4">
-        <v>0.73899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="E4">
-        <v>0.81699999999999995</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="F4">
-        <v>0.89100000000000001</v>
+        <v>0.89200000000000002</v>
       </c>
       <c r="G4">
-        <v>0.91400000000000003</v>
+        <v>0.91600000000000004</v>
       </c>
       <c r="H4">
         <v>0.96399999999999997</v>
@@ -526,39 +526,39 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>1.4E-2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.105</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.158</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.40400000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.2</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="B6">
         <v>0.434</v>
@@ -567,22 +567,22 @@
         <v>0.60399999999999998</v>
       </c>
       <c r="D6">
-        <v>0.77700000000000002</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="E6">
-        <v>0.83799999999999997</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="F6">
         <v>0.89100000000000001</v>
       </c>
       <c r="G6">
-        <v>0.95199999999999996</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="H6">
-        <v>0.97199999999999998</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="I6">
-        <v>0.99</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="J6">
         <v>0.996</v>
@@ -590,22 +590,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.189</v>
+        <v>0.187</v>
       </c>
       <c r="B7">
-        <v>0.41599999999999998</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="C7">
-        <v>0.57599999999999996</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="D7">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="E7">
-        <v>0.79600000000000004</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="F7">
-        <v>0.86799999999999999</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="G7">
         <v>0.93200000000000005</v>
@@ -625,19 +625,19 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="B8">
-        <v>0.38300000000000001</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="C8">
-        <v>0.54400000000000004</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="D8">
         <v>0.65900000000000003</v>
       </c>
       <c r="E8">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="F8">
-        <v>0.81</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="G8">
         <v>0.86099999999999999</v>
@@ -663,25 +663,25 @@
         <v>0.2</v>
       </c>
       <c r="D9">
-        <v>0.248</v>
+        <v>0.25</v>
       </c>
       <c r="E9">
-        <v>0.31</v>
+        <v>0.30599999999999999</v>
       </c>
       <c r="F9">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="G9">
-        <v>0.40400000000000003</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="H9">
-        <v>0.443</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="I9">
-        <v>0.504</v>
+        <v>0.50700000000000001</v>
       </c>
       <c r="J9">
-        <v>0.54800000000000004</v>
+        <v>0.55100000000000005</v>
       </c>
     </row>
   </sheetData>
